--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="10440"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -50,19 +50,19 @@
     <t>Class Code</t>
   </si>
   <si>
-    <t>&lt;&lt;e.g. SE1234&gt;&gt;</t>
+    <t>SE20C</t>
   </si>
   <si>
     <t>Semester</t>
   </si>
   <si>
-    <t>&lt;&lt;e.g. Fall 2026&gt;&gt;</t>
+    <t>Fall 2026</t>
   </si>
   <si>
     <t>Lecturer Name</t>
   </si>
   <si>
-    <t/>
+    <t>VinhNV27</t>
   </si>
   <si>
     <t>Group Code</t>
@@ -71,7 +71,7 @@
     <t>Project Title</t>
   </si>
   <si>
-    <t>&lt;&lt;e.g. AITA-mini: Assignment Submission &amp; Grading Portal&gt;&gt;</t>
+    <t>24/7 LLM Tutor (Cá nhân hóa lộ trình học tập FE-S-03)</t>
   </si>
   <si>
     <t>List of Student</t>
@@ -125,7 +125,7 @@
     <t>Nguyễn Anh Khoa</t>
   </si>
   <si>
-    <t>Chatgpt</t>
+    <t>Chatgpt, Gemini</t>
   </si>
   <si>
     <t>No.</t>
@@ -301,7 +301,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,13 +340,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -859,148 +852,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1440,8 +1433,8 @@
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>10</v>
+      <c r="B8" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5">

--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -205,6 +205,28 @@
   </si>
   <si>
     <t>Missing cascade delete rules</t>
+  </si>
+  <si>
+    <t>Database ERD schema design for AITA &amp; Group 6 (24/7 LLM Tutor - FE-S-03)</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated 8 3NF database tables (Roles, Users, Assignments, Submissions, Grades, Tutor_Sessions, Tutor_Messages, Personalized_Learning_Paths), Mermaid ERD diagram, and SQL Server DDL scripts.
+</t>
+  </si>
+  <si>
+    <t>Validated 3NF compliance, added SHA256_Hash UNIQUE constraint in Submissions table for security, added CHECK constraints for status fields, and linked optional FK submission_id to Tutor_Sessions.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link</t>
+  </si>
+  <si>
+    <t>8 entities, 9 relationships, 100% 3NF normalized.</t>
+  </si>
+  <si>
+    <t>Initial generated SQL script applied ON DELETE CASCADE directly on Users table which posed data loss risks; modified to RESTRICT / SET NULL constraints.</t>
   </si>
   <si>
     <t>&lt;&lt;sample data&gt;&gt;
@@ -335,6 +357,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
@@ -345,14 +375,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -867,12 +889,12 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -997,7 +1019,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1017,7 +1039,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1385,74 +1422,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1472,79 +1509,79 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="12">
+      <c r="A13" s="17">
         <v>1</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="14" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="12">
+      <c r="A14" s="17">
         <v>2</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="14" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" ht="26.4" spans="1:5">
-      <c r="A15" s="12">
+      <c r="A15" s="17">
         <v>3</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="12">
+      <c r="A16" s="17">
         <v>4</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="12">
+      <c r="A17" s="17">
         <v>5</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1566,8 +1603,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1677,7 +1714,42 @@
         <v>57</v>
       </c>
     </row>
+    <row r="4" ht="45" customHeight="1" spans="1:10">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="11">
+        <v>5</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G4" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1738,31 +1810,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:10">
@@ -1770,31 +1842,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1815,10 +1887,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1826,7 +1898,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:2">
@@ -1834,7 +1906,7 @@
         <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" ht="26.4" spans="1:2">
@@ -1842,7 +1914,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1850,7 +1922,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" ht="26.4" spans="1:2">
@@ -1858,7 +1930,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" ht="26.4" spans="1:2">
@@ -1866,7 +1938,7 @@
         <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="39.6" spans="1:2">
@@ -1874,7 +1946,7 @@
         <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="26.4" spans="1:2">
@@ -1882,7 +1954,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1890,7 +1962,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" ht="26.4" spans="1:2">
@@ -1898,7 +1970,7 @@
         <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="10440" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="99">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -227,6 +227,30 @@
   </si>
   <si>
     <t>Initial generated SQL script applied ON DELETE CASCADE directly on Users table which posed data loss risks; modified to RESTRICT / SET NULL constraints.</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>Business Logic Implementation for the 
+24/7 LLM Tutor module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created a 5-step flow: Student Request → Input Validation → Prompt Engineering → AI Service → Save &amp; Response. Suggested 4 input checks: non-empty, length, format, and rate limit.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked the AI flow with the project requirements and Java Web design. Made changes when needed.
+</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing</t>
+  </si>
+  <si>
+    <t>5 main steps; 4 validation checks; timeout + retry</t>
+  </si>
+  <si>
+    <t>Some suggested values may not fit the project. They need to be checked before implementation.</t>
   </si>
   <si>
     <t>&lt;&lt;sample data&gt;&gt;
@@ -1019,7 +1043,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1043,15 +1067,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1422,74 +1449,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1509,79 +1536,79 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="17">
+      <c r="A13" s="18">
         <v>1</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="17">
+      <c r="A14" s="18">
         <v>2</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" ht="26.4" spans="1:5">
-      <c r="A15" s="17">
+      <c r="A15" s="18">
         <v>3</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="17">
+      <c r="A16" s="18">
         <v>4</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="17">
+      <c r="A17" s="18">
         <v>5</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1603,8 +1630,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1718,37 +1745,70 @@
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="8">
         <v>5</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="5" ht="108" customHeight="1" spans="1:10">
+      <c r="A5" s="10">
+        <v>2</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="10">
+        <v>4</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
+    <hyperlink ref="G4" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
+    <hyperlink ref="G5" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1810,31 +1870,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:10">
@@ -1842,31 +1902,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1887,10 +1947,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1898,7 +1958,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:2">
@@ -1906,7 +1966,7 @@
         <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" ht="26.4" spans="1:2">
@@ -1914,7 +1974,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1922,7 +1982,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" ht="26.4" spans="1:2">
@@ -1930,7 +1990,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" ht="26.4" spans="1:2">
@@ -1938,7 +1998,7 @@
         <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" ht="39.6" spans="1:2">
@@ -1946,7 +2006,7 @@
         <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" ht="26.4" spans="1:2">
@@ -1954,7 +2014,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1962,7 +2022,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" ht="26.4" spans="1:2">
@@ -1970,7 +2030,7 @@
         <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -158,53 +158,7 @@
     <t>Risks / Limitations Observed</t>
   </si>
   <si>
-    <t>&lt;&lt;sample data&gt;&gt;
-Requirement</t>
-  </si>
-  <si>
-    <t>Use Case &amp; SRS drafting (Servlet/JSP scope)</t>
-  </si>
-  <si>
-    <t>ChatGPT</t>
-  </si>
-  <si>
-    <t>8 use cases + draft SRS outline</t>
-  </si>
-  <si>
-    <t>Kept 6 use cases, merged 2 duplicates, rewrote acceptance criteria</t>
-  </si>
-  <si>
-    <t>Google Doc link</t>
-  </si>
-  <si>
-    <t>6 use cases kept</t>
-  </si>
-  <si>
-    <t>Some use cases too generic, not FPT-specific</t>
-  </si>
-  <si>
     <t>Design</t>
-  </si>
-  <si>
-    <t>ERD for Submission/Grading module (reference: AITA Submission &amp; Rubric tables)</t>
-  </si>
-  <si>
-    <t>Copilot</t>
-  </si>
-  <si>
-    <t>Suggested 5 tables (User, Class, Assignment, Submission, Score)</t>
-  </si>
-  <si>
-    <t>Adjusted PK/FK, added AttemptNumber column, normalized to 3NF</t>
-  </si>
-  <si>
-    <t>draw.io link</t>
-  </si>
-  <si>
-    <t>5 entities, 6 relationships</t>
-  </si>
-  <si>
-    <t>Missing cascade delete rules</t>
   </si>
   <si>
     <t>Database ERD schema design for AITA &amp; Group 6 (24/7 LLM Tutor - FE-S-03)</t>
@@ -282,6 +236,9 @@
   </si>
   <si>
     <t>Test case generation for login &amp; submission upload</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
   </si>
   <si>
     <t>12 draft test cases (positive/negative)</t>
@@ -1043,7 +1000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1062,15 +1019,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1449,74 +1397,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1536,79 +1484,79 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="18">
+      <c r="A13" s="15">
         <v>1</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="18">
+      <c r="A14" s="15">
         <v>2</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" ht="26.4" spans="1:5">
-      <c r="A15" s="18">
+      <c r="A15" s="15">
         <v>3</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="12" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="18">
+      <c r="A16" s="15">
         <v>4</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="12" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="18">
+      <c r="A17" s="15">
         <v>5</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1630,8 +1578,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1677,138 +1625,74 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" ht="39.6" spans="1:10">
-      <c r="A2" s="5">
+    <row r="2" ht="96" customHeight="1" spans="1:10">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="8">
+        <v>5</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" ht="108" customHeight="1" spans="1:10">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="7">
         <v>4</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" ht="39.6" spans="1:10">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="I3" s="5">
-        <v>4</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1" spans="1:10">
-      <c r="A4" s="7">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" s="8">
-        <v>5</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" ht="108" customHeight="1" spans="1:10">
-      <c r="A5" s="10">
-        <v>2</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="I5" s="10">
-        <v>4</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
-    <hyperlink ref="G5" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1870,31 +1754,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:10">
@@ -1902,31 +1786,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1947,10 +1831,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1958,7 +1842,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:2">
@@ -1966,7 +1850,7 @@
         <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" ht="26.4" spans="1:2">
@@ -1974,7 +1858,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1982,7 +1866,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" ht="26.4" spans="1:2">
@@ -1990,7 +1874,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" ht="26.4" spans="1:2">
@@ -1998,7 +1882,7 @@
         <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" ht="39.6" spans="1:2">
@@ -2006,7 +1890,7 @@
         <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="26.4" spans="1:2">
@@ -2014,7 +1898,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2022,7 +1906,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" ht="26.4" spans="1:2">
@@ -2030,7 +1914,7 @@
         <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89887C2E-5743-4119-A9A4-222F106F90AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -21,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -292,19 +296,34 @@
   </si>
   <si>
     <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Analyze system requirements and define core features for the 24/7 LLM Tuto</t>
+  </si>
+  <si>
+    <t>Suggested problem statement, project objectives, and functional requirements including AI Tutor Chat, personalized learning recommendations, learning roadmap, progress tracking, and error explanation</t>
+  </si>
+  <si>
+    <t>Reviewed the AI suggestions and selected features suitable for the PRJ301 Java Web project scope. Removed overly complex features and refined the requirements based on the project objective</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing</t>
+  </si>
+  <si>
+    <t>11 features proposed, 8 core features selected</t>
+  </si>
+  <si>
+    <t>Some AI-generated requirements were too general or too complex and required manual review</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,36 +332,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -350,146 +376,18 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -520,194 +418,8 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -754,270 +466,31 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1026,79 +499,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1383,88 +829,113 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="15" t="s">
         <v>4</v>
       </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="15" t="s">
         <v>10</v>
       </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="15">
         <v>4</v>
       </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="15" t="s">
         <v>13</v>
       </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1484,102 +955,100 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="15">
+      <c r="A13" s="12">
         <v>1</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="15">
+      <c r="A14" s="12">
         <v>2</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="26.4" spans="1:5">
-      <c r="A15" s="15">
+    <row r="15" spans="1:5" ht="26.4">
+      <c r="A15" s="12">
         <v>3</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="15">
+      <c r="A16" s="12">
         <v>4</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="15">
+      <c r="A17" s="12">
         <v>5</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1593,7 +1062,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>32</v>
       </c>
@@ -1625,7 +1094,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="96" customHeight="1">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1657,7 +1126,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" ht="108" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="108" customHeight="1">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1685,25 +1154,56 @@
       <c r="I3" s="7">
         <v>4</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="115.2">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="19">
+        <v>4</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{F0A84737-78EB-406D-BE39-40AA88C2BC3C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1717,7 +1217,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>32</v>
       </c>
@@ -1749,7 +1249,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" ht="39.6" spans="1:10">
+    <row r="2" spans="1:10" ht="39.6">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1781,7 +1281,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" ht="26.4" spans="1:10">
+    <row r="3" spans="1:10" ht="26.4">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1815,15 +1315,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -1845,7 +1343,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" ht="26.4" spans="1:2">
+    <row r="3" spans="1:2" ht="26.4">
       <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
@@ -1853,7 +1351,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" ht="26.4" spans="1:2">
+    <row r="4" spans="1:2" ht="26.4">
       <c r="A4" s="2" t="s">
         <v>34</v>
       </c>
@@ -1869,7 +1367,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" ht="26.4" spans="1:2">
+    <row r="6" spans="1:2" ht="26.4">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -1877,7 +1375,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" ht="26.4" spans="1:2">
+    <row r="7" spans="1:2" ht="26.4">
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
@@ -1885,7 +1383,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" ht="39.6" spans="1:2">
+    <row r="8" spans="1:2" ht="39.6">
       <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
@@ -1893,7 +1391,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" ht="26.4" spans="1:2">
+    <row r="9" spans="1:2" ht="26.4">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
@@ -1909,7 +1407,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" ht="26.4" spans="1:2">
+    <row r="11" spans="1:2" ht="26.4">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
@@ -1919,6 +1417,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89887C2E-5743-4119-A9A4-222F106F90AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="10440" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -27,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -105,15 +101,18 @@
     <t>Menber</t>
   </si>
   <si>
+    <t>Gemini, Chatgpt, Claude</t>
+  </si>
+  <si>
+    <t>QE200054</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Duy</t>
+  </si>
+  <si>
     <t>Gemini, Chatgpt</t>
   </si>
   <si>
-    <t>QE200054</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Duy</t>
-  </si>
-  <si>
     <t>QE200113</t>
   </si>
   <si>
@@ -126,10 +125,19 @@
     <t>Copilot, Chatgpt, claude, antigravity</t>
   </si>
   <si>
+    <t>QE200060</t>
+  </si>
+  <si>
     <t>Nguyễn Anh Khoa</t>
   </si>
   <si>
     <t>Chatgpt, Gemini</t>
+  </si>
+  <si>
+    <t>QE200093</t>
+  </si>
+  <si>
+    <t>Nguyễn Nhật Tường Vy</t>
   </si>
   <si>
     <t>No.</t>
@@ -211,6 +219,30 @@
     <t>Some suggested values may not fit the project. They need to be checked before implementation.</t>
   </si>
   <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Analyze system requirements and define core features for the 24/7 LLM Tutor</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>Suggested problem statement, project objectives, and functional requirements including AI Tutor Chat, personalized learning recommendations, learning roadmap, progress tracking, and error explanation</t>
+  </si>
+  <si>
+    <t>Reviewed the AI suggestions and selected features suitable for the PRJ301 Java Web project scope. Removed overly complex features and refined the requirements based on the project objective</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing</t>
+  </si>
+  <si>
+    <t>11 features proposed, 8 core features selected</t>
+  </si>
+  <si>
+    <t>Some AI-generated requirements were too general or too complex and required manual review</t>
+  </si>
+  <si>
     <t>&lt;&lt;sample data&gt;&gt;
 Implementation</t>
   </si>
@@ -240,9 +272,6 @@
   </si>
   <si>
     <t>Test case generation for login &amp; submission upload</t>
-  </si>
-  <si>
-    <t>ChatGPT</t>
   </si>
   <si>
     <t>12 draft test cases (positive/negative)</t>
@@ -296,46 +325,24 @@
   </si>
   <si>
     <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
-  </si>
-  <si>
-    <t>Requirement</t>
-  </si>
-  <si>
-    <t>Analyze system requirements and define core features for the 24/7 LLM Tuto</t>
-  </si>
-  <si>
-    <t>Suggested problem statement, project objectives, and functional requirements including AI Tutor Chat, personalized learning recommendations, learning roadmap, progress tracking, and error explanation</t>
-  </si>
-  <si>
-    <t>Reviewed the AI suggestions and selected features suitable for the PRJ301 Java Web project scope. Removed overly complex features and refined the requirements based on the project objective</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing</t>
-  </si>
-  <si>
-    <t>11 features proposed, 8 core features selected</t>
-  </si>
-  <si>
-    <t>Some AI-generated requirements were too general or too complex and required manual review</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -343,32 +350,47 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -376,18 +398,146 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,8 +568,194 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -466,31 +802,270 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -499,52 +1074,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -829,113 +1440,88 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1">
+    <row r="1" ht="28.05" customHeight="1" spans="1:5">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="14" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="15">
         <v>4</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="14" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -955,100 +1541,112 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="12">
+      <c r="A13" s="18">
         <v>1</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="12">
+      <c r="A14" s="18">
         <v>2</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="26.4">
-      <c r="A15" s="12">
+      <c r="E14" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="26.4" spans="1:5">
+      <c r="A15" s="18">
         <v>3</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="B15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="C15" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="D15" s="15" t="s">
         <v>29</v>
       </c>
+      <c r="E15" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="12">
+      <c r="A16" s="18">
         <v>4</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="11" t="s">
+      <c r="B16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>31</v>
+      <c r="E16" s="15" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="12">
+      <c r="A17" s="18">
         <v>5</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+      <c r="B17" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1062,148 +1660,150 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="96" customHeight="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" ht="96" customHeight="1" spans="1:10">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I2" s="8">
         <v>5</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="108" customHeight="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" ht="108" customHeight="1" spans="1:10">
       <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I3" s="7">
         <v>4</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="115.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" ht="115.2" spans="1:10">
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="B4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="I4" s="19">
+      <c r="I4" s="10">
         <v>4</v>
       </c>
-      <c r="J4" s="20" t="s">
-        <v>91</v>
+      <c r="J4" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{F0A84737-78EB-406D-BE39-40AA88C2BC3C}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1217,111 +1817,113 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="39.6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" ht="39.6" spans="1:10">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="26.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" ht="26.4" spans="1:10">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -1329,93 +1931,94 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="26.4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" ht="26.4" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="26.4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" ht="26.4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="26.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" ht="26.4" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="26.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" ht="26.4" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="39.6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" ht="39.6" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="26.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" ht="26.4" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="26.4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" ht="26.4" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="10440" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
     <sheet name="1. Week 1" sheetId="2" r:id="rId2"/>
-    <sheet name="2. Week n" sheetId="3" r:id="rId3"/>
-    <sheet name="Instruction" sheetId="4" r:id="rId4"/>
+    <sheet name="1. Week 2" sheetId="5" r:id="rId3"/>
+    <sheet name="2. Week n" sheetId="3" r:id="rId4"/>
+    <sheet name="Instruction" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="96">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -337,7 +338,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,13 +375,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -918,133 +912,133 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1077,16 +1071,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1802,6 +1796,104 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" ht="121" customHeight="1" spans="1:10">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" ht="143" customHeight="1" spans="1:10">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" ht="139" customHeight="1" spans="1:10">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
@@ -1919,7 +2011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B11"/>

--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="102">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -242,6 +242,24 @@
   </si>
   <si>
     <t>Some AI-generated requirements were too general or too complex and required manual review</t>
+  </si>
+  <si>
+    <t>Drafting the core Software Requirement Specification (SRS) document for AITA - Group 6 (FE-S-03).</t>
+  </si>
+  <si>
+    <t>Generated the initial SRS framework (FRs, NFRs, Auth Matrix) and iteratively added advanced sections: Glossary, 3NF Data Requirements, Exception Paths, and Risk Mitigation strategies.</t>
+  </si>
+  <si>
+    <t>Reviewed against PRJ301 rubric. Manually structured 8 Use Cases, verified 8 entities against the team's ERD, and corrected the data loss mitigation strategy from ON DELETE CASCADE to ON DELETE RESTRICT.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1MvIEKYq72RDwufT_sIZ_XiyqlYSTz0PZ?usp=sharing</t>
+  </si>
+  <si>
+    <t>1 complete SRS document containing 6 main sections, 8 mapped Use Cases, 8 entities, and 3 risk strategies.</t>
+  </si>
+  <si>
+    <t>AI initially missed exception paths and suggested dangerous SQL constraints (CASCADE). Iterative prompting and manual corrections were required to meet academic standards.</t>
   </si>
   <si>
     <t>&lt;&lt;sample data&gt;&gt;
@@ -1042,7 +1060,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1067,6 +1085,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1448,74 +1469,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="16">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1535,87 +1556,87 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="18">
+      <c r="A13" s="19">
         <v>1</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="18">
+      <c r="A14" s="19">
         <v>2</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" ht="26.4" spans="1:5">
-      <c r="A15" s="18">
+      <c r="A15" s="19">
         <v>3</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="18">
+      <c r="A16" s="19">
         <v>4</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="16" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="18">
+      <c r="A17" s="19">
         <v>5</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="16" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1705,7 +1726,7 @@
       <c r="F2" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="8" t="s">
@@ -1737,7 +1758,7 @@
       <c r="F3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>58</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -1754,31 +1775,31 @@
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="11">
         <v>4</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1847,15 +1868,33 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="B2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="8">
+        <v>5</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="3" ht="143" customHeight="1" spans="1:10">
       <c r="A3" s="7">
@@ -1866,7 +1905,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
+      <c r="G3" s="10"/>
       <c r="H3" s="8"/>
       <c r="I3" s="7"/>
       <c r="J3" s="8"/>
@@ -1875,15 +1914,15 @@
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1946,31 +1985,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:10">
@@ -1978,31 +2017,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>63</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2023,10 +2062,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2034,7 +2073,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:2">
@@ -2042,7 +2081,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" ht="26.4" spans="1:2">
@@ -2050,7 +2089,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2058,7 +2097,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" ht="26.4" spans="1:2">
@@ -2066,7 +2105,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" ht="26.4" spans="1:2">
@@ -2074,7 +2113,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" ht="39.6" spans="1:2">
@@ -2082,7 +2121,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" ht="26.4" spans="1:2">
@@ -2090,7 +2129,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2098,7 +2137,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" ht="26.4" spans="1:2">
@@ -2106,7 +2145,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="10440" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="109">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -260,6 +260,27 @@
   </si>
   <si>
     <t>AI initially missed exception paths and suggested dangerous SQL constraints (CASCADE). Iterative prompting and manual corrections were required to meet academic standards.</t>
+  </si>
+  <si>
+    <t>Design MVC architecture and package structure for the 24/7 LLM Tutor module</t>
+  </si>
+  <si>
+    <t>ChatGPT, Gemini</t>
+  </si>
+  <si>
+    <t>Suggested an MVC structure with View (JSP), Controller (Servlet), Model (DTO/DAO), Service, and Filter layers, and explained how requests flow between the layers.</t>
+  </si>
+  <si>
+    <t>Reviewed the structure, verified package flow, and set up the Java Web project skeleton on VS Code matching PRJ301 standards.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1jfv8FE53NmF0-9jNc803u7VXSKQBN8MB?usp=sharing</t>
+  </si>
+  <si>
+    <t>5 main packages; 2 JSP pages; 5 main Java classes</t>
+  </si>
+  <si>
+    <t>The AI structure may not fully fit our project scope. Checked and adjusted package naming before project setup.</t>
   </si>
   <si>
     <t>&lt;&lt;sample data&gt;&gt;
@@ -1822,9 +1843,9 @@
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="3" max="3" width="38.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="31.4444444444444" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -1914,17 +1935,38 @@
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="12"/>
+      <c r="B4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="11">
+        <v>4</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G4" r:id="rId1" display="https://drive.google.com/drive/folders/1jfv8FE53NmF0-9jNc803u7VXSKQBN8MB?usp=sharing"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1985,31 +2027,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:10">
@@ -2017,31 +2059,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>63</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2062,10 +2104,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2073,7 +2115,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:2">
@@ -2081,7 +2123,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="26.4" spans="1:2">
@@ -2089,7 +2131,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2097,7 +2139,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="26.4" spans="1:2">
@@ -2105,7 +2147,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" ht="26.4" spans="1:2">
@@ -2113,7 +2155,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" ht="39.6" spans="1:2">
@@ -2121,7 +2163,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" ht="26.4" spans="1:2">
@@ -2129,7 +2171,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2137,7 +2179,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" ht="26.4" spans="1:2">
@@ -2145,7 +2187,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A1E0F9-B63A-4F16-BBF8-F4C60A4E4054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="10440" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -22,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="117">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -365,19 +369,37 @@
   </si>
   <si>
     <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
+  </si>
+  <si>
+    <t>System Design &amp; Implementation</t>
+  </si>
+  <si>
+    <t>Designing System Screen Flow Diagram (Draw.io) &amp; Constructing User Interface (UX/UI Design System &amp; SPA Layout)</t>
+  </si>
+  <si>
+    <t>Claude 3.5 / Antigravity / ChatGPT-4o</t>
+  </si>
+  <si>
+    <t>Role-based Navigation Screen Flow in Untitled Diagram.drawio (Student/Lecturer) and HTML/CSS/JS Dark Mode Glassmorphism UI code for 5 system view panels.</t>
+  </si>
+  <si>
+    <t>Added bidirectional navigation edges and role-differentiated color coding on Draw.io; refactored CSS Flexbox/Grid layouts, implemented smooth transitions, and fixed responsive overflow bugs on the Session History table.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1TsNLKc7zhuCoEUPjxf-lhVzScFA5SqKi?usp=sharing</t>
+  </si>
+  <si>
+    <t>Saved 70% of design time (~4.5 hours), delivered 100% complete interactive Screen Flow and responsive UI.</t>
+  </si>
+  <si>
+    <t>AI initially suggested overly complex UX flows, generated CSS with responsive overflow issues on smaller viewports, and lacked proper color contrast.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,36 +408,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -423,7 +452,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -431,146 +460,10 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -601,194 +494,8 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -835,270 +542,31 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1110,88 +578,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1476,88 +905,113 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>4</v>
       </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>6</v>
       </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="17" t="s">
         <v>10</v>
       </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="17">
         <v>4</v>
       </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>13</v>
       </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1577,112 +1031,110 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="19">
+      <c r="A13" s="14">
         <v>1</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="19">
+      <c r="A14" s="14">
         <v>2</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="26.4" spans="1:5">
-      <c r="A15" s="19">
+    <row r="15" spans="1:5" ht="26.4">
+      <c r="A15" s="14">
         <v>3</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="19">
+      <c r="A16" s="14">
         <v>4</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="13" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="19">
+      <c r="A17" s="14">
         <v>5</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="13" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1696,7 +1148,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -1728,7 +1180,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="96" customHeight="1">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1760,7 +1212,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" ht="108" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="108" customHeight="1">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1792,60 +1244,58 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" ht="115.2" spans="1:10">
+    <row r="4" spans="1:10" ht="115.2">
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="7">
         <v>4</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="8" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId1" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="38.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="31.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="31.44140625" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -1853,7 +1303,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -1885,7 +1335,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="121" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="121.05" customHeight="1">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1917,66 +1367,83 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" ht="143" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="142.94999999999999" customHeight="1">
       <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" ht="139" customHeight="1" spans="1:10">
+      <c r="B3" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I3" s="7">
+        <v>5</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="139.05000000000001" customHeight="1">
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="7">
         <v>4</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="8" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" display="https://drive.google.com/drive/folders/1jfv8FE53NmF0-9jNc803u7VXSKQBN8MB?usp=sharing"/>
+    <hyperlink ref="G4" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{88FF8E4D-AB20-4BD2-8574-82AFE88F9E13}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1990,7 +1457,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -2022,7 +1489,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" ht="39.6" spans="1:10">
+    <row r="2" spans="1:10" ht="39.6">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2054,7 +1521,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" ht="26.4" spans="1:10">
+    <row r="3" spans="1:10" ht="26.4">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2088,15 +1555,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -2118,7 +1583,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" ht="26.4" spans="1:2">
+    <row r="3" spans="1:2" ht="26.4">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
@@ -2126,7 +1591,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" ht="26.4" spans="1:2">
+    <row r="4" spans="1:2" ht="26.4">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
@@ -2142,7 +1607,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" ht="26.4" spans="1:2">
+    <row r="6" spans="1:2" ht="26.4">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -2150,7 +1615,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" ht="26.4" spans="1:2">
+    <row r="7" spans="1:2" ht="26.4">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -2158,7 +1623,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" ht="39.6" spans="1:2">
+    <row r="8" spans="1:2" ht="39.6">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
@@ -2166,7 +1631,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" ht="26.4" spans="1:2">
+    <row r="9" spans="1:2" ht="26.4">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -2182,7 +1647,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" ht="26.4" spans="1:2">
+    <row r="11" spans="1:2" ht="26.4">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -2192,6 +1657,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRJ301\PRJ---24-7-LLM-Tutor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A1E0F9-B63A-4F16-BBF8-F4C60A4E4054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4EE475-E647-4BB2-AD96-A73EA683F87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -19,23 +19,12 @@
     <sheet name="2. Week n" sheetId="3" r:id="rId4"/>
     <sheet name="Instruction" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="129">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -393,6 +382,42 @@
   </si>
   <si>
     <t>AI initially suggested overly complex UX flows, generated CSS with responsive overflow issues on smaller viewports, and lacked proper color contrast.</t>
+  </si>
+  <si>
+    <t>Design Use Case Diagram and 8 Use Case Specifications for the 24/7 LLM Tutor.</t>
+  </si>
+  <si>
+    <t>Generated the Use Case Diagram with 3 actors (Admin, Instructor, Student) and 8 use cases: UC01 Login &amp; Authorization, UC02 Manage User List, UC03 Manage Assignments, UC04 Submit ZIP &amp; SHA-256 Hashing, UC05 View Scores &amp; Feedback, UC06 Detect Error &amp; Initialize AI Session, UC07 Interact with 24/7 AI Tutor, and UC08 Get Personalized Learning Path. Generated detailed descriptions including main flows and exceptions for all 8 use cases.</t>
+  </si>
+  <si>
+    <t>Reviewed the generated use cases against the project requirements. Modified actor–use case relationships, use case names, main flows, and exception flows to match the AITA 24/7 LLM Tutor project.</t>
+  </si>
+  <si>
+    <t>3 actors, 8 use cases, 11 actor–use case associations, 8 detailed use case specifications</t>
+  </si>
+  <si>
+    <t>Some AI-generated use case relationships and descriptions may not fully match the project requirements and therefore required manual review and modification.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1_IiKnUxj3SQwrN2uhQHVUB0enmRgof_9?usp=sharing</t>
+  </si>
+  <si>
+    <t>Design Domain Model and ERD for the 24/7 LLM Tutor module</t>
+  </si>
+  <si>
+    <t>Generated a Domain Model and ERD structure for the core learning features, including Student, TutorConversation, TutorMessage, CodeError, LearningRecommendation, and LearningTopic, with suggested PK/FK relationships and cardinalities.</t>
+  </si>
+  <si>
+    <t>Compared the AI-generated model with the project Use Cases and requirements. Corrected entity responsibilities, PK/FK mapping, relationship cardinalities, and removed unnecessary attributes. Reviewed the model for 3NF consistency before preparing domain-model.md, erd.md, and README.md.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1Cv8UVkfH270j3_3KHpU-v4wu6AA63oxH?hl=vi</t>
+  </si>
+  <si>
+    <t>6 core entities; PK/FK and cardinalities defined; 3 documentation files prepared</t>
+  </si>
+  <si>
+    <t>AI initially suggested relationships and attributes that did not fully match the project's Use Cases. Manual review was required to correct cardinalities, foreign keys, and unnecessary data.</t>
   </si>
 </sst>
 </file>
@@ -549,7 +574,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -593,19 +618,40 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -919,99 +965,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="23">
         <v>4</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="27"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1288,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1354,7 +1400,7 @@
       <c r="F2" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>72</v>
       </c>
       <c r="H2" s="8" t="s">
@@ -1371,19 +1417,19 @@
       <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="15" t="s">
         <v>113</v>
       </c>
       <c r="G3" s="11" t="s">
@@ -1409,7 +1455,7 @@
       <c r="C4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="16" t="s">
         <v>76</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -1429,12 +1475,79 @@
       </c>
       <c r="J4" s="8" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="201.6">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" s="8">
+        <v>4</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="144">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" s="8">
+        <v>5</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G4" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{88FF8E4D-AB20-4BD2-8574-82AFE88F9E13}"/>
+    <hyperlink ref="G2" r:id="rId3" xr:uid="{501F067C-697C-4220-A862-1205015787E2}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{54149B39-3898-44D3-B264-6816775C6CC8}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{0587752F-533C-4EAB-B92A-01C112087A94}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRJ301\PRJ---24-7-LLM-Tutor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tuong Vy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4EE475-E647-4BB2-AD96-A73EA683F87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5137E93-4429-4649-8178-611F10AD2DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="2. Week n" sheetId="3" r:id="rId4"/>
     <sheet name="Instruction" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="123">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -400,24 +400,6 @@
   </si>
   <si>
     <t>https://drive.google.com/drive/folders/1_IiKnUxj3SQwrN2uhQHVUB0enmRgof_9?usp=sharing</t>
-  </si>
-  <si>
-    <t>Design Domain Model and ERD for the 24/7 LLM Tutor module</t>
-  </si>
-  <si>
-    <t>Generated a Domain Model and ERD structure for the core learning features, including Student, TutorConversation, TutorMessage, CodeError, LearningRecommendation, and LearningTopic, with suggested PK/FK relationships and cardinalities.</t>
-  </si>
-  <si>
-    <t>Compared the AI-generated model with the project Use Cases and requirements. Corrected entity responsibilities, PK/FK mapping, relationship cardinalities, and removed unnecessary attributes. Reviewed the model for 3NF consistency before preparing domain-model.md, erd.md, and README.md.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1Cv8UVkfH270j3_3KHpU-v4wu6AA63oxH?hl=vi</t>
-  </si>
-  <si>
-    <t>6 core entities; PK/FK and cardinalities defined; 3 documentation files prepared</t>
-  </si>
-  <si>
-    <t>AI initially suggested relationships and attributes that did not fully match the project's Use Cases. Manual review was required to correct cardinalities, foreign keys, and unnecessary data.</t>
   </si>
 </sst>
 </file>
@@ -574,7 +556,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -621,6 +603,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -629,18 +614,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -653,6 +626,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -965,99 +941,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="20">
         <v>4</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="27"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1455,7 +1431,7 @@
       <c r="C4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>76</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -1479,67 +1455,38 @@
     </row>
     <row r="5" spans="1:10" ht="201.6">
       <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="18" t="s">
         <v>120</v>
       </c>
       <c r="I5" s="8">
         <v>4</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="18" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="144">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="I6" s="8">
-        <v>5</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>128</v>
-      </c>
+    <row r="6" spans="1:10">
+      <c r="C6" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1547,7 +1494,6 @@
     <hyperlink ref="G3" r:id="rId2" xr:uid="{88FF8E4D-AB20-4BD2-8574-82AFE88F9E13}"/>
     <hyperlink ref="G2" r:id="rId3" xr:uid="{501F067C-697C-4220-A862-1205015787E2}"/>
     <hyperlink ref="G5" r:id="rId4" xr:uid="{54149B39-3898-44D3-B264-6816775C6CC8}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{0587752F-533C-4EAB-B92A-01C112087A94}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
